--- a/nonprofit_employee_forms/006_volunteer_appreciation_program_evaluation_form--nonprofit_employee_forms.xlsx
+++ b/nonprofit_employee_forms/006_volunteer_appreciation_program_evaluation_form--nonprofit_employee_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'volunteer'}</t>
+          <t>volunteer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Volunteer'}</t>
+          <t>Volunteer</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'non-board_member'}</t>
+          <t>non-board_member</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Non-Board Member'}</t>
+          <t>Non-Board Member</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'staff_member'}</t>
+          <t>staff_member</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Staff Member'}</t>
+          <t>Staff Member</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'publicly'}</t>
+          <t>publicly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Publicly'}</t>
+          <t>Publicly</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'privately'}</t>
+          <t>privately</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Privately'}</t>
+          <t>Privately</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'save_and_continue'}</t>
+          <t>save_and_continue</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Save and Continue'}</t>
+          <t>Save and Continue</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'save_and_edit'}</t>
+          <t>save_and_edit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Save and Edit'}</t>
+          <t>Save and Edit</t>
         </is>
       </c>
     </row>
